--- a/erp-server/erp-server-wms/src/main/resources/excel/deliveryPlanDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/deliveryPlanDetailTemplate.xlsx
@@ -661,10 +661,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>

--- a/erp-server/erp-server-wms/src/main/resources/excel/deliveryPlanDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/deliveryPlanDetailTemplate.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>SKU编号</t>
+    <t>第三方仓sku</t>
   </si>
   <si>
     <t>计划数量</t>
@@ -25,7 +38,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/deliveryPlanDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/deliveryPlanDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,19 @@
     <t>第三方仓sku</t>
   </si>
   <si>
-    <t>计划数量</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>计划数量</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -45,7 +57,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,6 +68,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -540,137 +559,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -678,6 +697,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1058,7 +1080,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/deliveryPlanDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/deliveryPlanDetailTemplate.xlsx
@@ -29,7 +29,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>第三方仓sku</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>第三方仓sku</t>
+    </r>
   </si>
   <si>
     <r>
@@ -689,14 +701,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1080,7 +1089,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
